--- a/deploy/093_ENT_CF/66 CF_I.xlsx
+++ b/deploy/093_ENT_CF/66 CF_I.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\deploy\093_ENT_CF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDA6FB62-3080-472A-B110-A8C821F7DD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF9F31E-D0CF-40A4-8725-A027E1BF0F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9290" yWindow="910" windowWidth="28800" windowHeight="15950" xr2:uid="{81579251-A4F3-427C-9337-0C346C834C3F}"/>
+    <workbookView xWindow="-27210" yWindow="3675" windowWidth="17280" windowHeight="10500" xr2:uid="{5BA75B06-F4D4-4189-B770-A2139C705C11}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="66 CF_I" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'66 CF_I'!$A$1:$A$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>TIPOOPERACION</t>
   </si>
@@ -71,64 +74,97 @@
     <t>MXN</t>
   </si>
   <si>
-    <t>ACR000000000000004</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000004</t>
   </si>
   <si>
-    <t>ACR000000000000007</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000007</t>
   </si>
   <si>
-    <t>ACR000000000000010</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000010</t>
   </si>
   <si>
-    <t>ACR000000000000006</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000006</t>
   </si>
   <si>
-    <t>ACR000000000000002</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000002</t>
   </si>
   <si>
-    <t>ACR000000000000009</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000009</t>
   </si>
   <si>
-    <t>ACR000000000000001</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000001</t>
   </si>
   <si>
-    <t>ACR000000000000005</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000005</t>
   </si>
   <si>
-    <t>ACR000000000000003</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000003</t>
   </si>
   <si>
-    <t>ACR000000000000008</t>
-  </si>
-  <si>
     <t>FOLIO00000000000000000000000000008</t>
+  </si>
+  <si>
+    <t>FOLIO00000000000000000000000000011</t>
+  </si>
+  <si>
+    <t>FOLIO00000000000000000000000000012</t>
+  </si>
+  <si>
+    <t>FOLIO00000000000000000000000000013</t>
+  </si>
+  <si>
+    <t>FOLIO00000000000000000000000000014</t>
+  </si>
+  <si>
+    <t>FOLIO00000000000000000000000000015</t>
+  </si>
+  <si>
+    <t>ACR004</t>
+  </si>
+  <si>
+    <t>ACR007</t>
+  </si>
+  <si>
+    <t>ACR010</t>
+  </si>
+  <si>
+    <t>ACR006</t>
+  </si>
+  <si>
+    <t>ACR002</t>
+  </si>
+  <si>
+    <t>ACR009</t>
+  </si>
+  <si>
+    <t>ACR001</t>
+  </si>
+  <si>
+    <t>ACR005</t>
+  </si>
+  <si>
+    <t>ACR003</t>
+  </si>
+  <si>
+    <t>ACR008</t>
+  </si>
+  <si>
+    <t>ACR011</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>ACR012</t>
+  </si>
+  <si>
+    <t>ACR013</t>
+  </si>
+  <si>
+    <t>ACR014</t>
+  </si>
+  <si>
+    <t>ACR015</t>
   </si>
 </sst>
 </file>
@@ -500,11 +536,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EFD146-3E47-4E30-A925-E449576F781B}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A58BCBB-840B-43DA-908E-64DA4E3B5737}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,15 +574,15 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -553,16 +600,16 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -582,16 +629,16 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -611,16 +658,16 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -640,16 +687,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -669,18 +716,18 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -698,16 +745,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -727,16 +774,16 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -756,16 +803,16 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>4</v>
       </c>
@@ -785,16 +832,16 @@
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10">
+        <v>33</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10">
         <v>4</v>
       </c>
-      <c r="I10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -814,13 +861,158 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46231</v>
+      </c>
+      <c r="E12">
+        <v>11000000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E13">
+        <v>12000000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E14">
+        <v>13000000</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E15">
+        <v>14000000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46192</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E16">
+        <v>15000000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
